--- a/Codelist Excel Files and Conversion Templates to XML/mwd_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/mwd_properties.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/Documents/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D922F2CB-9668-8B40-9878-FE0AF68C6936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0369E73-01C3-5144-B6ED-8AD15803327C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10820" yWindow="5040" windowWidth="42140" windowHeight="19460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51200" yWindow="620" windowWidth="38400" windowHeight="20980" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DictionaryName" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Lists" sheetId="5" r:id="rId4"/>
     <sheet name="Addtional Example" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="388">
   <si>
     <t>Description</t>
   </si>
@@ -1189,13 +1189,25 @@
   </si>
   <si>
     <t>Torque Tach</t>
+  </si>
+  <si>
+    <t>penetration_per_revolution</t>
+  </si>
+  <si>
+    <t>Penetration per revolution: the axial advance of the drill string or auger per full rotation of the drive - a feed-per-rotation efficiency indicator, distinct from penetration_rate (advance per unit time) and normally reported alongside rotational speed so the two can be cross-checked against each other.</t>
+  </si>
+  <si>
+    <t>Penetration per revolution</t>
+  </si>
+  <si>
+    <t>ancestor::diggs:constructionActivity//diggs:RIInstallationRecord</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1293,6 +1305,18 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF993300"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1373,7 +1397,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1448,23 +1472,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="11" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -1537,6 +1582,42 @@
         <vertAlign val="baseline"/>
         <color theme="0"/>
       </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1682,42 +1763,6 @@
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
   <extLst>
@@ -1732,46 +1777,46 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E3" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:E3" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H40" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
-  <autoFilter ref="A1:H40" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H38">
-    <sortCondition ref="C1:C38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H41" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:H41" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H41">
+    <sortCondition ref="B1:B41"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="12">
-      <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B2840,1,FALSE)),"Not used","")</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="19">
+      <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B2843,1,FALSE)),"Not used","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D40" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:D40" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C2">
-    <sortCondition ref="C1:C2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D46" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:D46" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D44">
+    <sortCondition ref="B1:B44"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Start" dataDxfId="3">
@@ -2127,7 +2172,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="14" customWidth="1"/>
@@ -2169,7 +2214,7 @@
     </row>
     <row r="2" spans="1:8" ht="136" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B2875,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B2878,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B2" s="15" t="s">
@@ -2193,7 +2238,7 @@
     </row>
     <row r="3" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B3,AssociatedElements!B$2:B2884,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B3,AssociatedElements!B$2:B2887,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B3" s="15" t="s">
@@ -2211,7 +2256,7 @@
     </row>
     <row r="4" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B4,AssociatedElements!B$2:B2841,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B4,AssociatedElements!B$2:B2844,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B4" s="15" t="s">
@@ -2232,7 +2277,7 @@
     </row>
     <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B5,AssociatedElements!B$2:B2845,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B5,AssociatedElements!B$2:B2848,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B5" s="15" t="s">
@@ -2252,283 +2297,274 @@
       </c>
       <c r="G5" s="19"/>
     </row>
-    <row r="6" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B6,AssociatedElements!B$2:B2844,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B6,AssociatedElements!B$2:B2857,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B6" s="15" t="s">
-        <v>288</v>
+        <v>377</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>289</v>
+        <v>378</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>285</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="221" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B7,AssociatedElements!B$2:B2872,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B7,AssociatedElements!B$2:B2880,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B7" s="15" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>356</v>
+        <v>248</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>305</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="H7" s="28" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="170" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="221" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B8,AssociatedElements!B$2:B2877,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B8,AssociatedElements!B$2:B2875,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B8" s="15" t="s">
-        <v>340</v>
+        <v>263</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>341</v>
+        <v>245</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>1</v>
       </c>
+      <c r="F8" s="14" t="s">
+        <v>3</v>
+      </c>
       <c r="G8" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>355</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B9,AssociatedElements!B$2:B2845,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B9,AssociatedElements!B$2:B2880,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B9" s="15" t="s">
-        <v>253</v>
+        <v>374</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>237</v>
+        <v>375</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+      <c r="G9" s="19"/>
+    </row>
+    <row r="10" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B10,AssociatedElements!B$2:B2846,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B10,AssociatedElements!B$2:B2874,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B10" s="15" t="s">
-        <v>254</v>
+        <v>322</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>238</v>
+        <v>315</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="170" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B11,AssociatedElements!B$2:B2844,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B11,AssociatedElements!B$2:B2880,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B11" s="15" t="s">
-        <v>252</v>
+        <v>340</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>236</v>
+        <v>341</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>302</v>
+        <v>342</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="F11" s="14" t="s">
-        <v>162</v>
+      <c r="G11" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B12,AssociatedElements!B$2:B2847,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B12,AssociatedElements!B$2:B2848,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B12" s="15" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>303</v>
+        <v>237</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>344</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B13,AssociatedElements!B$2:B2859,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B13,AssociatedElements!B$2:B2849,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B13" s="15" t="s">
-        <v>292</v>
+        <v>254</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>293</v>
+        <v>238</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>306</v>
+        <v>345</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="G13" s="19"/>
-    </row>
-    <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B14,AssociatedElements!B$2:B2874,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B14,AssociatedElements!B$2:B2847,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B14" s="15" t="s">
-        <v>327</v>
+        <v>252</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>328</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>329</v>
+        <v>236</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>302</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="19"/>
-    </row>
-    <row r="15" spans="1:8" ht="119" x14ac:dyDescent="0.2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B15,AssociatedElements!B$2:B2876,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B15,AssociatedElements!B$2:B2850,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B15" s="15" t="s">
-        <v>343</v>
+        <v>255</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>338</v>
+        <v>239</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>339</v>
+        <v>303</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="G15" s="19" t="s">
-        <v>364</v>
-      </c>
-      <c r="H15" s="29" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="F15" s="14" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B16,AssociatedElements!B$2:B2873,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B16,AssociatedElements!B$2:B2879,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B16" s="15" t="s">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>326</v>
+        <v>360</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>373</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="G16" s="19"/>
     </row>
-    <row r="17" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B17,AssociatedElements!B$2:B2865,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B17,AssociatedElements!B$2:B2862,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B17" s="15" t="s">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>307</v>
+        <v>293</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>306</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+      <c r="G17" s="19"/>
+    </row>
+    <row r="18" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B18,AssociatedElements!B$2:B2864,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B18,AssociatedElements!B$2:B2877,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B18" s="15" t="s">
-        <v>259</v>
+        <v>327</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>308</v>
+        <v>328</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>329</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>1</v>
@@ -2536,263 +2572,266 @@
       <c r="F18" s="14" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="30" t="str">
-        <f>IF(ISNA(VLOOKUP(B19,AssociatedElements!B$2:B2857,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B19" t="s">
-        <v>261</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>381</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>382</v>
-      </c>
-      <c r="E19" s="33" t="s">
+      <c r="G18" s="19"/>
+    </row>
+    <row r="19" spans="1:8" ht="119" x14ac:dyDescent="0.2">
+      <c r="A19" s="14" t="str">
+        <f>IF(ISNA(VLOOKUP(B19,AssociatedElements!B$2:B2879,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="E19" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="F19" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="G19" s="35"/>
-      <c r="H19" s="34"/>
-    </row>
-    <row r="20" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="G19" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B20,AssociatedElements!B$2:B2848,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B20,AssociatedElements!B$2:B2876,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B20" s="15" t="s">
-        <v>256</v>
+        <v>324</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>309</v>
+        <v>325</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>326</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="G20" s="19"/>
+    </row>
+    <row r="21" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B21,AssociatedElements!B$2:B2849,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B21,AssociatedElements!B$2:B2868,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B21" s="15" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B22,AssociatedElements!B$2:B2854,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>377</v>
+        <f>IF(ISNA(VLOOKUP(B22,AssociatedElements!B$2:B2860,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B22" t="s">
+        <v>261</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>285</v>
+        <v>382</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+        <v>162</v>
+      </c>
+      <c r="G22" s="19"/>
+    </row>
+    <row r="23" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B23,AssociatedElements!B$2:B2853,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B23,AssociatedElements!B$2:B2867,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B23" s="15" t="s">
-        <v>25</v>
+        <v>259</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>346</v>
+        <v>242</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>308</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B24,AssociatedElements!B$2:B2872,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B24,AssociatedElements!B$2:B2851,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B24" s="20" t="s">
-        <v>321</v>
+        <v>256</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>323</v>
+        <v>296</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>309</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="19"/>
+        <v>17</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B25,AssociatedElements!B$2:B2871,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B25,AssociatedElements!B$2:B2852,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B25" s="15" t="s">
-        <v>322</v>
+        <v>257</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>316</v>
+        <v>240</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>310</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>174</v>
+        <v>1</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B26,AssociatedElements!B$2:B2852,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>258</v>
+        <f>IF(ISNA(VLOOKUP(B26,AssociatedElements!B$2:B2875,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B26" s="40" t="s">
+        <v>321</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>311</v>
+        <v>320</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>323</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="G26" s="19"/>
+    </row>
+    <row r="27" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B27,AssociatedElements!B$2:B2842,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B27,AssociatedElements!B$2:B2855,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B27" s="15" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="221" x14ac:dyDescent="0.2">
-      <c r="A28" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B28,AssociatedElements!B$2:B2874,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>357</v>
-      </c>
-      <c r="E28" s="17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+      <c r="A28" s="31" t="str">
+        <f>IF(ISNA(VLOOKUP(B28,AssociatedElements!B$2:B2882,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>385</v>
+      </c>
+      <c r="E28" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="F28" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="F28" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="35"/>
+      <c r="H28" s="34"/>
+    </row>
+    <row r="29" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B29,AssociatedElements!B$2:B2843,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B29,AssociatedElements!B$2:B2845,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B29" s="15" t="s">
-        <v>286</v>
+        <v>251</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>297</v>
+        <v>235</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="221" x14ac:dyDescent="0.2">
       <c r="A30" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B30,AssociatedElements!B$2:B2874,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B30,AssociatedElements!B$2:B2877,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B30" s="15" t="s">
-        <v>332</v>
+        <v>265</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>333</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>363</v>
+        <v>247</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>334</v>
+        <v>21</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>358</v>
@@ -2801,232 +2840,260 @@
         <v>370</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="119" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B31,AssociatedElements!B$2:B2873,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B31,AssociatedElements!B$2:B2846,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B31" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>246</v>
+        <v>286</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>297</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>361</v>
+        <v>287</v>
       </c>
       <c r="E31" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="G31" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="H31" s="27" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="153" x14ac:dyDescent="0.2">
+      <c r="F31" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A32" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B32,AssociatedElements!B$2:B2871,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B32,AssociatedElements!B$2:B2847,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B32" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>244</v>
+        <v>288</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>319</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>353</v>
+        <v>289</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="H32" s="27" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="221" x14ac:dyDescent="0.2">
       <c r="A33" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B33,AssociatedElements!B$2:B2878,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B33,AssociatedElements!B$2:B2877,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B33" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>348</v>
+        <v>332</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>333</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>313</v>
+        <v>363</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="G33" s="19"/>
-    </row>
-    <row r="34" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="119" x14ac:dyDescent="0.2">
       <c r="A34" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B34,AssociatedElements!B$2:B2840,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B34,AssociatedElements!B$2:B2876,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B34" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>349</v>
-      </c>
-      <c r="E34" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="E34" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="F34" s="14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="G34" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="H34" s="27" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="153" x14ac:dyDescent="0.2">
       <c r="A35" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B35,AssociatedElements!B$2:B2879,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B35,AssociatedElements!B$2:B2874,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B35" s="15" t="s">
-        <v>291</v>
+        <v>262</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>383</v>
-      </c>
-      <c r="D35" s="24" t="s">
-        <v>295</v>
+        <v>244</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>353</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="19"/>
-    </row>
-    <row r="36" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="H35" s="27" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B36,AssociatedElements!B$2:B2850,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B36,AssociatedElements!B$2:B2881,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B36" s="15" t="s">
-        <v>299</v>
+        <v>347</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+      <c r="G36" s="19"/>
+    </row>
+    <row r="37" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A37" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B37,AssociatedElements!B$2:B2871,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B37,AssociatedElements!B$2:B2856,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B37" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>301</v>
+        <v>25</v>
+      </c>
+      <c r="C37" s="41" t="s">
+        <v>379</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B38,AssociatedElements!B$2:B2877,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B38,AssociatedElements!B$2:B2843,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B38" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>248</v>
+        <v>249</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>233</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="E38" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="E38" s="21" t="s">
         <v>1</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B39,AssociatedElements!B$2:B2876,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B39,AssociatedElements!B$2:B2882,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B39" s="15" t="s">
-        <v>359</v>
+        <v>291</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>360</v>
-      </c>
-      <c r="D39" s="22" t="s">
-        <v>373</v>
+        <v>383</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>295</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G39" s="19"/>
     </row>
-    <row r="40" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="14" t="str">
-        <f>IF(ISNA(VLOOKUP(B40,AssociatedElements!B$2:B2877,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B40,AssociatedElements!B$2:B2853,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B40" s="15" t="s">
-        <v>374</v>
+        <v>299</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>375</v>
+        <v>331</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>376</v>
+        <v>298</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="G40" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A41" s="14" t="str">
+        <f>IF(ISNA(VLOOKUP(B41,AssociatedElements!B$2:B2874,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{4E4F4386-7FD3-DF49-A4FA-813DAEC4C0E2}"/>
-    <hyperlink ref="H7" r:id="rId2" xr:uid="{19D7D6E5-5ACE-324A-8460-A6F4DDD4E28B}"/>
-    <hyperlink ref="H8" r:id="rId3" xr:uid="{57F0ED7A-11F4-D240-AD82-9CE55AE72124}"/>
-    <hyperlink ref="H15" r:id="rId4" xr:uid="{8D50C3BF-C589-C14D-B41C-E99AE03A2CDC}"/>
-    <hyperlink ref="H31" r:id="rId5" xr:uid="{FC3D442E-4CC0-0847-A941-C36DD2CE39AF}"/>
-    <hyperlink ref="H32" r:id="rId6" xr:uid="{0FF5AB1B-449D-8843-B572-B81E096359CD}"/>
+    <hyperlink ref="H8" r:id="rId2" xr:uid="{19D7D6E5-5ACE-324A-8460-A6F4DDD4E28B}"/>
+    <hyperlink ref="H11" r:id="rId3" xr:uid="{57F0ED7A-11F4-D240-AD82-9CE55AE72124}"/>
+    <hyperlink ref="H19" r:id="rId4" xr:uid="{8D50C3BF-C589-C14D-B41C-E99AE03A2CDC}"/>
+    <hyperlink ref="H34" r:id="rId5" xr:uid="{FC3D442E-4CC0-0847-A941-C36DD2CE39AF}"/>
+    <hyperlink ref="H35" r:id="rId6" xr:uid="{0FF5AB1B-449D-8843-B572-B81E096359CD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId7"/>
@@ -3057,7 +3124,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
@@ -3080,13 +3147,13 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <f>IF(ISNA(VLOOKUP(B2,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B2" t="s">
-        <v>249</v>
+      <c r="B2" s="10" t="s">
+        <v>335</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>314</v>
@@ -3095,13 +3162,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>IF(ISNA(VLOOKUP(B3,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B3" t="s">
-        <v>250</v>
+      <c r="B3" s="10" t="s">
+        <v>284</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>314</v>
@@ -3116,7 +3183,7 @@
         <v/>
       </c>
       <c r="B4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>314</v>
@@ -3125,13 +3192,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>IF(ISNA(VLOOKUP(B5,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B5" t="s">
-        <v>252</v>
+      <c r="B5" s="10" t="s">
+        <v>290</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>314</v>
@@ -3146,7 +3213,7 @@
         <v/>
       </c>
       <c r="B6" t="s">
-        <v>253</v>
+        <v>377</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>314</v>
@@ -3161,7 +3228,7 @@
         <v/>
       </c>
       <c r="B7" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>314</v>
@@ -3176,7 +3243,7 @@
         <v/>
       </c>
       <c r="B8" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>314</v>
@@ -3185,13 +3252,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <f>IF(ISNA(VLOOKUP(B9,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B9" t="s">
-        <v>256</v>
+      <c r="B9" s="10" t="s">
+        <v>374</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>314</v>
@@ -3200,13 +3267,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
         <f>IF(ISNA(VLOOKUP(B10,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B10" t="s">
-        <v>257</v>
+      <c r="B10" s="10" t="s">
+        <v>322</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>314</v>
@@ -3215,13 +3282,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f>IF(ISNA(VLOOKUP(B11,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B11" t="s">
-        <v>258</v>
+      <c r="B11" s="10" t="s">
+        <v>340</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>314</v>
@@ -3236,7 +3303,7 @@
         <v/>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>253</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>314</v>
@@ -3251,7 +3318,7 @@
         <v/>
       </c>
       <c r="B13" t="s">
-        <v>377</v>
+        <v>254</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>314</v>
@@ -3266,7 +3333,7 @@
         <v/>
       </c>
       <c r="B14" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>314</v>
@@ -3281,7 +3348,7 @@
         <v/>
       </c>
       <c r="B15" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>314</v>
@@ -3290,13 +3357,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <f>IF(ISNA(VLOOKUP(B16,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B16" t="s">
-        <v>261</v>
+      <c r="B16" s="10" t="s">
+        <v>359</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>314</v>
@@ -3305,13 +3372,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
         <f>IF(ISNA(VLOOKUP(B17,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B17" t="s">
-        <v>262</v>
+      <c r="B17" s="10" t="s">
+        <v>292</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>314</v>
@@ -3320,13 +3387,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
         <f>IF(ISNA(VLOOKUP(B18,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B18" t="s">
-        <v>263</v>
+      <c r="B18" s="10" t="s">
+        <v>327</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>314</v>
@@ -3335,13 +3402,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
         <f>IF(ISNA(VLOOKUP(B19,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B19" t="s">
-        <v>264</v>
+      <c r="B19" s="10" t="s">
+        <v>343</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>314</v>
@@ -3350,13 +3417,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
         <f>IF(ISNA(VLOOKUP(B20,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B20" t="s">
-        <v>265</v>
+      <c r="B20" s="10" t="s">
+        <v>324</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>314</v>
@@ -3371,7 +3438,7 @@
         <v/>
       </c>
       <c r="B21" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>314</v>
@@ -3380,13 +3447,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
         <f>IF(ISNA(VLOOKUP(B22,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>347</v>
+      <c r="B22" t="s">
+        <v>261</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>314</v>
@@ -3395,13 +3462,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
         <f>IF(ISNA(VLOOKUP(B23,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>291</v>
+      <c r="B23" t="s">
+        <v>259</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>314</v>
@@ -3410,13 +3477,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
         <f>IF(ISNA(VLOOKUP(B24,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>284</v>
+      <c r="B24" t="s">
+        <v>256</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>314</v>
@@ -3425,13 +3492,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
         <f>IF(ISNA(VLOOKUP(B25,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>290</v>
+      <c r="B25" t="s">
+        <v>257</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>314</v>
@@ -3446,7 +3513,7 @@
         <v/>
       </c>
       <c r="B26" s="10" t="s">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>314</v>
@@ -3455,13 +3522,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
         <f>IF(ISNA(VLOOKUP(B27,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>288</v>
+      <c r="B27" t="s">
+        <v>258</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>314</v>
@@ -3471,57 +3538,57 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" t="str">
+      <c r="A28" s="37" t="str">
         <f>IF(ISNA(VLOOKUP(B28,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="B28" s="38" t="s">
+        <v>384</v>
+      </c>
+      <c r="C28" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="39" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" t="str">
+      <c r="A29" s="37" t="str">
         <f>IF(ISNA(VLOOKUP(B29,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="B29" s="38" t="s">
+        <v>384</v>
+      </c>
+      <c r="C29" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="D29" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" t="str">
+      <c r="D29" s="36" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="37" t="str">
         <f>IF(ISNA(VLOOKUP(B30,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>300</v>
+      <c r="B30" t="s">
+        <v>251</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D30" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="D30" s="36" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
         <f>IF(ISNA(VLOOKUP(B31,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>327</v>
+      <c r="B31" t="s">
+        <v>251</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>314</v>
@@ -3530,13 +3597,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
         <f>IF(ISNA(VLOOKUP(B32,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>324</v>
+      <c r="B32" t="s">
+        <v>265</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>314</v>
@@ -3551,7 +3618,7 @@
         <v/>
       </c>
       <c r="B33" s="10" t="s">
-        <v>321</v>
+        <v>286</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>314</v>
@@ -3566,7 +3633,7 @@
         <v/>
       </c>
       <c r="B34" s="10" t="s">
-        <v>322</v>
+        <v>288</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>314</v>
@@ -3590,13 +3657,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
         <f>IF(ISNA(VLOOKUP(B36,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>335</v>
+      <c r="B36" t="s">
+        <v>264</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>314</v>
@@ -3605,13 +3672,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
         <f>IF(ISNA(VLOOKUP(B37,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>343</v>
+      <c r="B37" t="s">
+        <v>262</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>314</v>
@@ -3626,7 +3693,7 @@
         <v/>
       </c>
       <c r="B38" s="10" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>314</v>
@@ -3635,13 +3702,13 @@
         <v>380</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
         <f>IF(ISNA(VLOOKUP(B39,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>359</v>
+      <c r="B39" t="s">
+        <v>25</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>314</v>
@@ -3650,19 +3717,109 @@
         <v>380</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
         <f>IF(ISNA(VLOOKUP(B40,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>374</v>
+      <c r="B40" t="s">
+        <v>249</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>314</v>
       </c>
       <c r="D40" t="s">
         <v>380</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="37" t="str">
+        <f>IF(ISNA(VLOOKUP(B41,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B41" t="s">
+        <v>249</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D41" s="36" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A42" t="str">
+        <f>IF(ISNA(VLOOKUP(B42,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D42" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A43" t="str">
+        <f>IF(ISNA(VLOOKUP(B43,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D43" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A44" t="str">
+        <f>IF(ISNA(VLOOKUP(B44,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D44" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A45" s="37" t="str">
+        <f>IF(ISNA(VLOOKUP(B45,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B45" s="44" t="s">
+        <v>286</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D45" s="36" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A46" s="37" t="str">
+        <f>IF(ISNA(VLOOKUP(B46,Definitions!B$2:B$1823,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B46" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D46" s="36" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
